--- a/data/tags/אלבומים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-06-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מייזי פיטרס Florescence</v>
+        <v>פרויקט אסי עזר - כל מה שעוזר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%99%d7%96%d7%99-%d7%a4%d7%99%d7%98%d7%a8%d7%a1-florescence/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24473&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>החיים נראים מעט אחרת עבור מייזי פיטרס. מאז יציאת  אלבומה השני, "The Good Witch" מ-2023.  באלבומה השלישי, כוכבת הפופ הבריטית משחררת את הכאב ומוצאת שלווה באהבת אמת. בדיוק כשהקריירה שלה צברה תאוצה לקראת סוף 2024, הזמרת שנבחרה לחמם את ההופעות</v>
+        <v>19:49</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מייזי פיטרס Florescence</v>
+        <v>פרויקט אסי עזר - כל מה שעוזר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-06-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרויקט אסי עזר - כל מה שעוזר</v>
+        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24473&amp;forum=music&amp;viewmode=all</v>
+        <v>https://yosmusic.com/%d7%90%d7%9c%d7%91%d7%95%d7%9d-%d7%94%d7%a4%d7%a1%d7%a7%d7%95%d7%9c-%d7%94%d7%a8%d7%a9%d7%9e%d7%99-%d7%a9%d7%9c-%d7%92%d7%91%d7%99%d7%a2-%d7%94%d7%a2%d7%95%d7%9c%d7%9d-%d7%91%d7%9b%d7%93%d7%95%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>19:49</v>
+        <v>זהן אוסף בן שעה אחת ו־18 רצועות, המורכב ברובו משיתופי פעולה בין אמנים שנעים בין סטורמזי ושאקירה לבין ג'לי רול והרולינג סטונז? לאורך השנים נוצרה הרבה מוזיקה בהשראת כדורגל. אבל האם נמצא ממנה משהו כאן שהופך את האוסף למיוחד בסוגו?</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרויקט אסי עזר - כל מה שעוזר</v>
+        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/אלבומים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/אלבומים חדשים/global/2026-06-week01/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
+        <v>נינט טייב - אני נינה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%9c%d7%91%d7%95%d7%9d-%d7%94%d7%a4%d7%a1%d7%a7%d7%95%d7%9c-%d7%94%d7%a8%d7%a9%d7%9e%d7%99-%d7%a9%d7%9c-%d7%92%d7%91%d7%99%d7%a2-%d7%94%d7%a2%d7%95%d7%9c%d7%9d-%d7%91%d7%9b%d7%93%d7%95%d7%a8/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24474&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>זהן אוסף בן שעה אחת ו־18 רצועות, המורכב ברובו משיתופי פעולה בין אמנים שנעים בין סטורמזי ושאקירה לבין ג'לי רול והרולינג סטונז? לאורך השנים נוצרה הרבה מוזיקה בהשראת כדורגל. אבל האם נמצא ממנה משהו כאן שהופך את האוסף למיוחד בסוגו?</v>
+        <v>09:26</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אלבום הפסקול הרשמי של גביע העולם בכדורגל 2026 של פיפ"א</v>
+        <v>נינט טייב - אני נינה</v>
       </c>
     </row>
   </sheetData>
